--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4E8C6AB-0A20-42CA-B827-2005F3000035}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E0D81B-45BE-4E8C-80C7-A0668B2AD8A9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1560,10 +1560,18 @@
       </c>
       <c r="AK7" s="19"/>
       <c r="AL7" s="20"/>
-      <c r="AM7" s="21"/>
-      <c r="AN7" s="22"/>
-      <c r="AO7" s="32"/>
-      <c r="AP7" s="32"/>
+      <c r="AM7" s="21">
+        <v>7</v>
+      </c>
+      <c r="AN7" s="22">
+        <v>5</v>
+      </c>
+      <c r="AO7" s="32">
+        <v>6</v>
+      </c>
+      <c r="AP7" s="32">
+        <v>2</v>
+      </c>
       <c r="AQ7" s="24"/>
       <c r="AR7" s="25"/>
     </row>
@@ -1872,10 +1880,18 @@
       </c>
       <c r="M11" s="47"/>
       <c r="N11" s="48"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="45"/>
+      <c r="O11" s="44">
+        <v>5</v>
+      </c>
+      <c r="P11" s="45">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="46">
+        <v>2</v>
+      </c>
+      <c r="R11" s="45">
+        <v>6</v>
+      </c>
       <c r="S11" s="47"/>
       <c r="T11" s="48"/>
       <c r="U11" s="44"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E0D81B-45BE-4E8C-80C7-A0668B2AD8A9}"/>
+  <xr:revisionPtr revIDLastSave="220" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E107D7B7-C63B-4B10-B0FC-B5517964BF6A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1738,10 +1738,18 @@
       </c>
       <c r="AK9" s="40"/>
       <c r="AL9" s="41"/>
-      <c r="AM9" s="21"/>
-      <c r="AN9" s="22"/>
-      <c r="AO9" s="23"/>
-      <c r="AP9" s="22"/>
+      <c r="AM9" s="21">
+        <v>6</v>
+      </c>
+      <c r="AN9" s="22">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="23">
+        <v>6</v>
+      </c>
+      <c r="AP9" s="22">
+        <v>3</v>
+      </c>
       <c r="AQ9" s="24"/>
       <c r="AR9" s="25"/>
     </row>
@@ -1900,10 +1908,18 @@
       <c r="X11" s="45"/>
       <c r="Y11" s="47"/>
       <c r="Z11" s="49"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="45"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="45"/>
+      <c r="AA11" s="44">
+        <v>4</v>
+      </c>
+      <c r="AB11" s="45">
+        <v>6</v>
+      </c>
+      <c r="AC11" s="46">
+        <v>3</v>
+      </c>
+      <c r="AD11" s="45">
+        <v>6</v>
+      </c>
       <c r="AE11" s="47"/>
       <c r="AF11" s="48"/>
       <c r="AG11" s="50">

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E107D7B7-C63B-4B10-B0FC-B5517964BF6A}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CF03EDB-90C9-41B9-A3BC-C942BC8DB1AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1651,10 +1651,18 @@
       <c r="AL8" s="20">
         <v>10</v>
       </c>
-      <c r="AM8" s="21"/>
-      <c r="AN8" s="22"/>
-      <c r="AO8" s="23"/>
-      <c r="AP8" s="22"/>
+      <c r="AM8" s="21">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="22">
+        <v>6</v>
+      </c>
+      <c r="AO8" s="23">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="22">
+        <v>6</v>
+      </c>
       <c r="AQ8" s="33"/>
       <c r="AR8" s="34"/>
     </row>
@@ -1902,10 +1910,18 @@
       </c>
       <c r="S11" s="47"/>
       <c r="T11" s="48"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="45"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="45"/>
+      <c r="U11" s="44">
+        <v>6</v>
+      </c>
+      <c r="V11" s="45">
+        <v>1</v>
+      </c>
+      <c r="W11" s="46">
+        <v>6</v>
+      </c>
+      <c r="X11" s="45">
+        <v>4</v>
+      </c>
       <c r="Y11" s="47"/>
       <c r="Z11" s="49"/>
       <c r="AA11" s="44">
